--- a/data/trans_orig/MCS12_SP_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2007</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>509273</t>
+          <t>508133</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>575863</t>
+          <t>573687</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>701184</t>
+          <t>704699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>775025</t>
+          <t>772229</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1229523</t>
+          <t>1232126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1330650</t>
+          <t>1328712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>455860</t>
+          <t>458036</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>522450</t>
+          <t>523590</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>540088</t>
+          <t>542884</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>613929</t>
+          <t>610414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1016185</t>
+          <t>1018123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1117312</t>
+          <t>1114709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>618267</t>
+          <t>618829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>704953</t>
+          <t>698643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>798710</t>
+          <t>798168</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>880509</t>
+          <t>878468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1445149</t>
+          <t>1438529</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1556880</t>
+          <t>1556711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>988460</t>
+          <t>994770</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1075146</t>
+          <t>1074584</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>707164</t>
+          <t>709205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>788963</t>
+          <t>789505</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1724206</t>
+          <t>1724375</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1835937</t>
+          <t>1842557</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>191362</t>
+          <t>193844</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>238144</t>
+          <t>239729</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>229027</t>
+          <t>231584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>272946</t>
+          <t>276623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>435663</t>
+          <t>437454</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>504473</t>
+          <t>505293</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313264</t>
+          <t>311679</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>360046</t>
+          <t>357564</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>203466</t>
+          <t>199789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>247385</t>
+          <t>244828</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>523347</t>
+          <t>522527</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>592157</t>
+          <t>590366</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1356877</t>
+          <t>1359326</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1473889</t>
+          <t>1474346</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1773088</t>
+          <t>1770768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1890301</t>
+          <t>1893868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3167492</t>
+          <t>3159395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3328852</t>
+          <t>3321312</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1802654</t>
+          <t>1802197</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1919666</t>
+          <t>1917217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1488896</t>
+          <t>1485329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1606109</t>
+          <t>1608429</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3326889</t>
+          <t>3334429</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3488249</t>
+          <t>3496346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,53%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2012</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>498318</t>
+          <t>501943</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>563555</t>
+          <t>562188</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>862940</t>
+          <t>865034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>930937</t>
+          <t>932512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1379826</t>
+          <t>1376829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1481263</t>
+          <t>1475856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,82%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411088</t>
+          <t>412455</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>476325</t>
+          <t>472700</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>406860</t>
+          <t>405285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>474857</t>
+          <t>472763</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>831177</t>
+          <t>836584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>932614</t>
+          <t>935611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,46%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>883440</t>
+          <t>880203</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>970298</t>
+          <t>970981</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1007612</t>
+          <t>1007212</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1089573</t>
+          <t>1090524</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1910661</t>
+          <t>1909347</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2038375</t>
+          <t>2032774</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>993659</t>
+          <t>992976</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1080517</t>
+          <t>1083754</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>668230</t>
+          <t>667279</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>750191</t>
+          <t>750591</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1683385</t>
+          <t>1688986</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1811099</t>
+          <t>1812413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>193571</t>
+          <t>193191</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>242086</t>
+          <t>240648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>225852</t>
+          <t>226841</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>271832</t>
+          <t>271749</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>431856</t>
+          <t>434921</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>498733</t>
+          <t>495131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,68%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239095</t>
+          <t>240533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287610</t>
+          <t>287990</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>186799</t>
+          <t>186882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>232779</t>
+          <t>231790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>441080</t>
+          <t>444682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>507957</t>
+          <t>504892</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,72%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1611248</t>
+          <t>1610904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1736600</t>
+          <t>1730035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2139583</t>
+          <t>2137010</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2263492</t>
+          <t>2255042</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3773341</t>
+          <t>3789296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3950958</t>
+          <t>3961085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1683182</t>
+          <t>1689747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1808534</t>
+          <t>1808878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1290738</t>
+          <t>1299188</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1414647</t>
+          <t>1417220</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3023054</t>
+          <t>3012927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3200671</t>
+          <t>3184716</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2016</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>396993</t>
+          <t>399093</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>453442</t>
+          <t>450819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>582063</t>
+          <t>582358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>644113</t>
+          <t>646744</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>999836</t>
+          <t>999630</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1082553</t>
+          <t>1078301</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300905</t>
+          <t>303528</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>357354</t>
+          <t>355254</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>350547</t>
+          <t>347916</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>412597</t>
+          <t>412302</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>666454</t>
+          <t>670706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749171</t>
+          <t>749377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>905075</t>
+          <t>914134</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>999809</t>
+          <t>1003764</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>999484</t>
+          <t>1001695</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1089548</t>
+          <t>1086706</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1930492</t>
+          <t>1937096</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2064432</t>
+          <t>2062081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1076576</t>
+          <t>1072621</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1171310</t>
+          <t>1162251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>898752</t>
+          <t>901594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>988816</t>
+          <t>986605</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2000253</t>
+          <t>2002604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2134193</t>
+          <t>2127589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>220203</t>
+          <t>221958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>267494</t>
+          <t>271145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>255310</t>
+          <t>253188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>303102</t>
+          <t>300986</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>485914</t>
+          <t>490477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>554259</t>
+          <t>558198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,93%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279392</t>
+          <t>275741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>326683</t>
+          <t>324928</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246038</t>
+          <t>248154</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>293830</t>
+          <t>295952</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>541768</t>
+          <t>537829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>610113</t>
+          <t>605550</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1560023</t>
+          <t>1569706</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1682211</t>
+          <t>1684356</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1876160</t>
+          <t>1876517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1998774</t>
+          <t>2002321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3473358</t>
+          <t>3468221</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3648077</t>
+          <t>3649275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1695407</t>
+          <t>1693262</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1817595</t>
+          <t>1807912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1533326</t>
+          <t>1529779</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1655940</t>
+          <t>1655583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3261641</t>
+          <t>3260443</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3436360</t>
+          <t>3441497</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,81%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2023</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>242932</t>
+          <t>243203</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>284195</t>
+          <t>285505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>441906</t>
+          <t>440774</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>481488</t>
+          <t>482626</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>696690</t>
+          <t>695166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>756245</t>
+          <t>754936</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,11%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>226201</t>
+          <t>224891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267464</t>
+          <t>267193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264068</t>
+          <t>262930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303650</t>
+          <t>304782</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>499706</t>
+          <t>501015</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>559261</t>
+          <t>560785</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>570385</t>
+          <t>567993</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>919412</t>
+          <t>917638</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1030592</t>
+          <t>1038404</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1484331</t>
+          <t>1472903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1666873</t>
+          <t>1693295</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2321619</t>
+          <t>2325306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,52%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1362134</t>
+          <t>1363908</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1711161</t>
+          <t>1713553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>747765</t>
+          <t>759193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1201504</t>
+          <t>1193692</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2192023</t>
+          <t>2188336</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2846769</t>
+          <t>2820347</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,48%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>239058</t>
+          <t>238358</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>293845</t>
+          <t>294590</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>291164</t>
+          <t>291994</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>337387</t>
+          <t>336895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>543189</t>
+          <t>542927</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>616426</t>
+          <t>611821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>46,99%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>350616</t>
+          <t>349871</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>405403</t>
+          <t>406103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>320202</t>
+          <t>320694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>366425</t>
+          <t>365595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>685624</t>
+          <t>690229</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>758861</t>
+          <t>759123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1004857</t>
+          <t>1057783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1448320</t>
+          <t>1452426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1828160</t>
+          <t>1825405</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2327713</t>
+          <t>2245288</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2968104</t>
+          <t>2968782</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3572404</t>
+          <t>3630588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1988083</t>
+          <t>1983977</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2431546</t>
+          <t>2378620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1307527</t>
+          <t>1389952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1807080</t>
+          <t>1809835</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3499239</t>
+          <t>3441055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4103539</t>
+          <t>4102861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/MCS12_SP_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>508133</t>
+          <t>510560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>573687</t>
+          <t>576629</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>704699</t>
+          <t>701889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>772229</t>
+          <t>771943</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1232126</t>
+          <t>1229144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1328712</t>
+          <t>1326962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>458036</t>
+          <t>455094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>523590</t>
+          <t>521163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>542884</t>
+          <t>543170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>610414</t>
+          <t>613224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1018123</t>
+          <t>1019873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1114709</t>
+          <t>1117691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,63%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>618829</t>
+          <t>617200</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>698643</t>
+          <t>697461</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>798168</t>
+          <t>799854</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>878468</t>
+          <t>879269</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1438529</t>
+          <t>1441821</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1556711</t>
+          <t>1554370</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,37%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>994770</t>
+          <t>995952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1074584</t>
+          <t>1076213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>709205</t>
+          <t>708404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>789505</t>
+          <t>787819</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1724375</t>
+          <t>1726716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1842557</t>
+          <t>1839265</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>193844</t>
+          <t>194137</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>239729</t>
+          <t>241770</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>231584</t>
+          <t>232965</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>276623</t>
+          <t>277642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>437454</t>
+          <t>438106</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>505293</t>
+          <t>504932</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311679</t>
+          <t>309638</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>357564</t>
+          <t>357271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>199789</t>
+          <t>198770</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244828</t>
+          <t>243447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>522527</t>
+          <t>522888</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>590366</t>
+          <t>589714</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,38%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1359326</t>
+          <t>1359732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1474346</t>
+          <t>1472819</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1770768</t>
+          <t>1773654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1893868</t>
+          <t>1890895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3159395</t>
+          <t>3161364</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3321312</t>
+          <t>3326987</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1802197</t>
+          <t>1803724</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1917217</t>
+          <t>1916811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1485329</t>
+          <t>1488302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1608429</t>
+          <t>1605543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3334429</t>
+          <t>3328754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3496346</t>
+          <t>3494377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,5%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>501943</t>
+          <t>498068</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>562188</t>
+          <t>561517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>865034</t>
+          <t>863015</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>932512</t>
+          <t>932865</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1376829</t>
+          <t>1379765</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1475856</t>
+          <t>1478736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,95%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412455</t>
+          <t>413126</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>472700</t>
+          <t>476575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>405285</t>
+          <t>404932</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>472763</t>
+          <t>474782</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>836584</t>
+          <t>833704</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>935611</t>
+          <t>932675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>880203</t>
+          <t>881914</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>970981</t>
+          <t>969725</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1007212</t>
+          <t>1005668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1090524</t>
+          <t>1086176</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1909347</t>
+          <t>1908983</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2032774</t>
+          <t>2039437</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>992976</t>
+          <t>994232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1083754</t>
+          <t>1082043</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>667279</t>
+          <t>671627</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>750591</t>
+          <t>752135</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1688986</t>
+          <t>1682323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1812413</t>
+          <t>1812777</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>193191</t>
+          <t>191988</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>240648</t>
+          <t>238103</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>226841</t>
+          <t>228005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>271749</t>
+          <t>272037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>434921</t>
+          <t>430970</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>495131</t>
+          <t>499930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>53,19%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>240533</t>
+          <t>243078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287990</t>
+          <t>289193</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>186882</t>
+          <t>186594</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231790</t>
+          <t>230626</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>444682</t>
+          <t>439883</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>504892</t>
+          <t>508843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>54,14%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1610904</t>
+          <t>1611880</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1730035</t>
+          <t>1733851</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2137010</t>
+          <t>2134713</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2255042</t>
+          <t>2261141</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3789296</t>
+          <t>3776659</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3961085</t>
+          <t>3954011</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1689747</t>
+          <t>1685931</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1808878</t>
+          <t>1807902</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1299188</t>
+          <t>1293089</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1417220</t>
+          <t>1419517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3012927</t>
+          <t>3020001</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3184716</t>
+          <t>3197353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>399093</t>
+          <t>398683</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>450819</t>
+          <t>452735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>582358</t>
+          <t>584585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>646744</t>
+          <t>645433</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>999630</t>
+          <t>997113</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1078301</t>
+          <t>1080939</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,8%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303528</t>
+          <t>301612</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>355254</t>
+          <t>355664</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>347916</t>
+          <t>349227</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>412302</t>
+          <t>410075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670706</t>
+          <t>668068</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749377</t>
+          <t>751894</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>914134</t>
+          <t>912581</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1003764</t>
+          <t>1006467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1001695</t>
+          <t>1004104</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1086706</t>
+          <t>1091454</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1937096</t>
+          <t>1926606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2062081</t>
+          <t>2060254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,69%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1072621</t>
+          <t>1069918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1162251</t>
+          <t>1163804</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>901594</t>
+          <t>896846</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>986605</t>
+          <t>984196</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2002604</t>
+          <t>2004431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2127589</t>
+          <t>2138079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,6%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221958</t>
+          <t>218777</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>271145</t>
+          <t>269192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>253188</t>
+          <t>255203</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>300986</t>
+          <t>302218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>490477</t>
+          <t>489250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>558198</t>
+          <t>555107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275741</t>
+          <t>277694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324928</t>
+          <t>328109</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>248154</t>
+          <t>246922</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>295952</t>
+          <t>293937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>537829</t>
+          <t>540920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>605550</t>
+          <t>606777</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,36%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1569706</t>
+          <t>1565764</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1684356</t>
+          <t>1683443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1876517</t>
+          <t>1873580</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2002321</t>
+          <t>1997096</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3468221</t>
+          <t>3479820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3649275</t>
+          <t>3648160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1693262</t>
+          <t>1694175</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1807912</t>
+          <t>1811854</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1529779</t>
+          <t>1535004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1655583</t>
+          <t>1658520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3260443</t>
+          <t>3261558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3441497</t>
+          <t>3429898</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>264622</t>
+          <t>285741</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>243203</t>
+          <t>263446</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>285505</t>
+          <t>309794</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>461719</t>
+          <t>501677</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>440774</t>
+          <t>477971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>482626</t>
+          <t>522659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>726340</t>
+          <t>787418</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>695166</t>
+          <t>755318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>754936</t>
+          <t>818179</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,07%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>245774</t>
+          <t>287848</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224891</t>
+          <t>263795</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267193</t>
+          <t>310143</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>283837</t>
+          <t>309795</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>262930</t>
+          <t>288813</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304782</t>
+          <t>333501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>529611</t>
+          <t>597643</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>501015</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>560785</t>
+          <t>629743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>45,47%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>510396</t>
+          <t>573589</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>510396</t>
+          <t>573589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>510396</t>
+          <t>573589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>745556</t>
+          <t>811472</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>745556</t>
+          <t>811472</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>745556</t>
+          <t>811472</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1255951</t>
+          <t>1385061</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1255951</t>
+          <t>1385061</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1255951</t>
+          <t>1385061</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>798879</t>
+          <t>887951</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>567993</t>
+          <t>842746</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>917638</t>
+          <t>943079</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1182106</t>
+          <t>1023723</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1038404</t>
+          <t>978892</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1472903</t>
+          <t>1069441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1980985</t>
+          <t>1911674</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1693295</t>
+          <t>1836014</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2325306</t>
+          <t>1974369</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1482667</t>
+          <t>1333016</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1363908</t>
+          <t>1277888</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1713553</t>
+          <t>1378221</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1049990</t>
+          <t>1141697</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>759193</t>
+          <t>1095979</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1193692</t>
+          <t>1186528</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2532657</t>
+          <t>2474714</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2188336</t>
+          <t>2412019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2820347</t>
+          <t>2550374</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2281546</t>
+          <t>2220967</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2281546</t>
+          <t>2220967</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2281546</t>
+          <t>2220967</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2232096</t>
+          <t>2165420</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2232096</t>
+          <t>2165420</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2232096</t>
+          <t>2165420</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4513642</t>
+          <t>4386388</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4513642</t>
+          <t>4386388</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4513642</t>
+          <t>4386388</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>264832</t>
+          <t>293152</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>238358</t>
+          <t>262586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>294590</t>
+          <t>319102</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>314279</t>
+          <t>358254</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>291994</t>
+          <t>334584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>336895</t>
+          <t>381363</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>579112</t>
+          <t>651407</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>542927</t>
+          <t>616201</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>611821</t>
+          <t>689131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>379629</t>
+          <t>415982</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>349871</t>
+          <t>390032</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>406103</t>
+          <t>446548</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>343310</t>
+          <t>373537</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>320694</t>
+          <t>350428</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>365595</t>
+          <t>397207</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>722938</t>
+          <t>789518</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>690229</t>
+          <t>751794</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>759123</t>
+          <t>824724</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>57,24%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>644461</t>
+          <t>709134</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>644461</t>
+          <t>709134</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644461</t>
+          <t>709134</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>657589</t>
+          <t>731791</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>657589</t>
+          <t>731791</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>657589</t>
+          <t>731791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1302050</t>
+          <t>1440925</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1302050</t>
+          <t>1440925</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1302050</t>
+          <t>1440925</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1328333</t>
+          <t>1466845</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1057783</t>
+          <t>1404371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1452426</t>
+          <t>1528960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1958104</t>
+          <t>1883653</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1825405</t>
+          <t>1826009</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2245288</t>
+          <t>1937038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3286436</t>
+          <t>3350498</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2968782</t>
+          <t>3274349</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3630588</t>
+          <t>3444789</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2108070</t>
+          <t>2036846</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1983977</t>
+          <t>1974731</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2378620</t>
+          <t>2099320</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1677136</t>
+          <t>1825030</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1389952</t>
+          <t>1771645</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1809835</t>
+          <t>1882674</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3785207</t>
+          <t>3861876</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3441055</t>
+          <t>3767585</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4102861</t>
+          <t>3938025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3436403</t>
+          <t>3503691</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3436403</t>
+          <t>3503691</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3436403</t>
+          <t>3503691</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3635240</t>
+          <t>3708683</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3635240</t>
+          <t>3708683</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3635240</t>
+          <t>3708683</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7071643</t>
+          <t>7212374</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7071643</t>
+          <t>7212374</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7071643</t>
+          <t>7212374</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
